--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487553_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487553_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>5.8156</v>
+        <v>6.7472</v>
       </c>
       <c r="E2" t="n">
-        <v>6.1206</v>
+        <v>6.9987</v>
       </c>
       <c r="F2" t="n">
-        <v>-0.305</v>
+        <v>-0.2515</v>
       </c>
       <c r="G2" t="n">
         <v>7.074</v>
@@ -610,13 +610,13 @@
         <v>3.1336</v>
       </c>
       <c r="S2" t="n">
-        <v>-1.3706</v>
+        <v>-0.439</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.9328</v>
+        <v>-0.0547</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.4378</v>
+        <v>-0.3843</v>
       </c>
       <c r="V2" t="n">
         <v>-1.0629</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>5.7547</v>
+        <v>5.6896</v>
       </c>
       <c r="E3" t="n">
-        <v>5.0757</v>
+        <v>4.9304</v>
       </c>
       <c r="F3" t="n">
-        <v>0.679</v>
+        <v>0.7592</v>
       </c>
       <c r="G3" t="n">
         <v>3.9263</v>
@@ -688,13 +688,13 @@
         <v>2.1543</v>
       </c>
       <c r="S3" t="n">
-        <v>0.0711</v>
+        <v>0.006</v>
       </c>
       <c r="T3" t="n">
-        <v>0.4911</v>
+        <v>0.3458</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.42</v>
+        <v>-0.3398</v>
       </c>
       <c r="V3" t="n">
         <v>-0.397</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>5.4628</v>
+        <v>4.1583</v>
       </c>
       <c r="E4" t="n">
-        <v>5.0559</v>
+        <v>4.3395</v>
       </c>
       <c r="F4" t="n">
-        <v>0.4069</v>
+        <v>-0.1812</v>
       </c>
       <c r="G4" t="n">
         <v>3.3954</v>
@@ -766,13 +766,13 @@
         <v>1.3709</v>
       </c>
       <c r="S4" t="n">
-        <v>1.4959</v>
+        <v>0.1914</v>
       </c>
       <c r="T4" t="n">
-        <v>1.4703</v>
+        <v>0.754</v>
       </c>
       <c r="U4" t="n">
-        <v>0.0255</v>
+        <v>-0.5625</v>
       </c>
       <c r="V4" t="n">
         <v>1.159</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>2.1072</v>
+        <v>2.3888</v>
       </c>
       <c r="E5" t="n">
-        <v>2.1923</v>
+        <v>2.661</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.0851</v>
+        <v>-0.2722</v>
       </c>
       <c r="G5" t="n">
         <v>1.6653</v>
@@ -844,13 +844,13 @@
         <v>2.3502</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.2371</v>
+        <v>0.0446</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.7546</v>
+        <v>-0.2858</v>
       </c>
       <c r="U5" t="n">
-        <v>0.5175</v>
+        <v>0.3304</v>
       </c>
       <c r="V5" t="n">
         <v>-1.6712</v>
@@ -877,10 +877,10 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>1.5959</v>
+        <v>1.6982</v>
       </c>
       <c r="E6" t="n">
-        <v>2.3015</v>
+        <v>2.4038</v>
       </c>
       <c r="F6" t="n">
         <v>-0.7056</v>
@@ -922,10 +922,10 @@
         <v>1.9585</v>
       </c>
       <c r="S6" t="n">
-        <v>0.1123</v>
+        <v>0.2147</v>
       </c>
       <c r="T6" t="n">
-        <v>0.9069</v>
+        <v>1.0092</v>
       </c>
       <c r="U6" t="n">
         <v>-0.7946</v>
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.6942</v>
+        <v>0.8338</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.0524</v>
+        <v>0.0071</v>
       </c>
       <c r="F7" t="n">
-        <v>0.7466</v>
+        <v>0.8268</v>
       </c>
       <c r="G7" t="n">
         <v>3.0086</v>
@@ -1000,13 +1000,13 @@
         <v>1.3709</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.7476</v>
+        <v>-0.608</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.5764</v>
+        <v>-0.517</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.1712</v>
+        <v>-0.091</v>
       </c>
       <c r="V7" t="n">
         <v>0</v>
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.1804</v>
+        <v>0.2068</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.5602</v>
+        <v>-0.2532</v>
       </c>
       <c r="F8" t="n">
-        <v>0.3798</v>
+        <v>0.46</v>
       </c>
       <c r="G8" t="n">
         <v>-1.1119</v>
@@ -1078,13 +1078,13 @@
         <v>1.1751</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.2435</v>
+        <v>0.1437</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.3211</v>
+        <v>-0.0141</v>
       </c>
       <c r="U8" t="n">
-        <v>0.0776</v>
+        <v>0.1578</v>
       </c>
       <c r="V8" t="n">
         <v>0</v>
@@ -1099,7 +1099,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A. FILGUEIRA BUCETA</t>
+          <t>A. BOUZAN CUMPLIDO</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1111,73 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.9493</v>
+        <v>-0.5750999999999999</v>
       </c>
       <c r="E9" t="n">
-        <v>0.9765</v>
+        <v>0.5389</v>
       </c>
       <c r="F9" t="n">
-        <v>-1.9257</v>
+        <v>-1.114</v>
       </c>
       <c r="G9" t="n">
-        <v>-1.7393</v>
+        <v>-0.2984</v>
       </c>
       <c r="H9" t="n">
-        <v>-1.5676</v>
+        <v>0.3093</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.1717</v>
+        <v>-0.6077</v>
       </c>
       <c r="J9" t="n">
-        <v>-0.2581</v>
+        <v>1.5704</v>
       </c>
       <c r="K9" t="n">
-        <v>-0.3437</v>
+        <v>1.1228</v>
       </c>
       <c r="L9" t="n">
-        <v>0.0857</v>
+        <v>0.4475</v>
       </c>
       <c r="M9" t="n">
-        <v>-1.4812</v>
+        <v>-1.8687</v>
       </c>
       <c r="N9" t="n">
-        <v>-1.2239</v>
+        <v>-0.8135</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.2573</v>
+        <v>-1.0552</v>
       </c>
       <c r="P9" t="n">
-        <v>0.1958</v>
+        <v>1.7626</v>
       </c>
       <c r="Q9" t="n">
         <v>-0.9792</v>
       </c>
       <c r="R9" t="n">
-        <v>1.1751</v>
+        <v>2.7419</v>
       </c>
       <c r="S9" t="n">
-        <v>1.8683</v>
+        <v>-0.9765</v>
       </c>
       <c r="T9" t="n">
-        <v>2.2714</v>
+        <v>-0.3276</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.403</v>
+        <v>-0.6489</v>
       </c>
       <c r="V9" t="n">
-        <v>-1.2742</v>
+        <v>-1.0629</v>
       </c>
       <c r="W9" t="n">
-        <v>-0.0576</v>
+        <v>0.2754</v>
       </c>
       <c r="X9" t="n">
-        <v>-1.2166</v>
+        <v>-1.3383</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A. BOUZAN CUMPLIDO</t>
+          <t>A. ALVAREZ JORGE</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,73 +1189,73 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.982</v>
+        <v>-1.4957</v>
       </c>
       <c r="E10" t="n">
-        <v>0.4795</v>
+        <v>-1.4833</v>
       </c>
       <c r="F10" t="n">
-        <v>-1.4615</v>
+        <v>-0.0125</v>
       </c>
       <c r="G10" t="n">
-        <v>-0.2984</v>
+        <v>-1.6322</v>
       </c>
       <c r="H10" t="n">
-        <v>0.3093</v>
+        <v>0</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.6077</v>
+        <v>-1.6322</v>
       </c>
       <c r="J10" t="n">
-        <v>1.5704</v>
+        <v>-1.3645</v>
       </c>
       <c r="K10" t="n">
-        <v>1.1228</v>
+        <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>0.4475</v>
+        <v>-1.3645</v>
       </c>
       <c r="M10" t="n">
-        <v>-1.8687</v>
+        <v>-0.2677</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.8135</v>
+        <v>0</v>
       </c>
       <c r="O10" t="n">
-        <v>-1.0552</v>
+        <v>-0.2677</v>
       </c>
       <c r="P10" t="n">
-        <v>1.7626</v>
+        <v>0.3917</v>
       </c>
       <c r="Q10" t="n">
-        <v>-0.9792</v>
+        <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>2.7419</v>
+        <v>0.3917</v>
       </c>
       <c r="S10" t="n">
-        <v>-1.3834</v>
+        <v>-0.2553</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.387</v>
+        <v>-0.1188</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.9964</v>
+        <v>-0.1364</v>
       </c>
       <c r="V10" t="n">
-        <v>-1.0629</v>
+        <v>0</v>
       </c>
       <c r="W10" t="n">
-        <v>0.2754</v>
+        <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>-1.3383</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A. ALVAREZ JORGE</t>
+          <t>A. FILGUEIRA BUCETA</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,67 +1267,67 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-1.4957</v>
+        <v>-2.204</v>
       </c>
       <c r="E11" t="n">
-        <v>-1.4833</v>
+        <v>-0.2516</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.0125</v>
+        <v>-1.9525</v>
       </c>
       <c r="G11" t="n">
-        <v>-1.6322</v>
+        <v>-1.7393</v>
       </c>
       <c r="H11" t="n">
-        <v>0</v>
+        <v>-1.5676</v>
       </c>
       <c r="I11" t="n">
-        <v>-1.6322</v>
+        <v>-0.1717</v>
       </c>
       <c r="J11" t="n">
-        <v>-1.3645</v>
+        <v>-0.2581</v>
       </c>
       <c r="K11" t="n">
-        <v>0</v>
+        <v>-0.3437</v>
       </c>
       <c r="L11" t="n">
-        <v>-1.3645</v>
+        <v>0.0857</v>
       </c>
       <c r="M11" t="n">
-        <v>-0.2677</v>
+        <v>-1.4812</v>
       </c>
       <c r="N11" t="n">
-        <v>0</v>
+        <v>-1.2239</v>
       </c>
       <c r="O11" t="n">
-        <v>-0.2677</v>
+        <v>-0.2573</v>
       </c>
       <c r="P11" t="n">
-        <v>0.3917</v>
+        <v>0.1958</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>-0.9792</v>
       </c>
       <c r="R11" t="n">
-        <v>0.3917</v>
+        <v>1.1751</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.2553</v>
+        <v>0.6136</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.1188</v>
+        <v>1.0433</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.1364</v>
+        <v>-0.4298</v>
       </c>
       <c r="V11" t="n">
-        <v>0</v>
+        <v>-1.2742</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>-0.0576</v>
       </c>
       <c r="X11" t="n">
-        <v>0</v>
+        <v>-1.2166</v>
       </c>
     </row>
     <row r="12">
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-3.5997</v>
+        <v>-2.9277</v>
       </c>
       <c r="E12" t="n">
-        <v>-1.1076</v>
+        <v>-0.5959</v>
       </c>
       <c r="F12" t="n">
-        <v>-2.4922</v>
+        <v>-2.3318</v>
       </c>
       <c r="G12" t="n">
         <v>-2.6825</v>
@@ -1390,13 +1390,13 @@
         <v>0.7834</v>
       </c>
       <c r="S12" t="n">
-        <v>-1.0923</v>
+        <v>-0.4202</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.517</v>
+        <v>-0.0053</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.5753</v>
+        <v>-0.4149</v>
       </c>
       <c r="V12" t="n">
         <v>-0.6083</v>
@@ -1423,10 +1423,10 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>14.2233</v>
+        <v>14.5202</v>
       </c>
       <c r="E13" t="n">
-        <v>18.9985</v>
+        <v>19.2954</v>
       </c>
       <c r="F13" t="n">
         <v>-4.7753</v>
@@ -1435,7 +1435,7 @@
         <v>10.7393</v>
       </c>
       <c r="H13" t="n">
-        <v>0.005199999999999538</v>
+        <v>0.005199999999999871</v>
       </c>
       <c r="I13" t="n">
         <v>10.7341</v>
@@ -1468,13 +1468,13 @@
         <v>18.6056</v>
       </c>
       <c r="S13" t="n">
-        <v>-1.7822</v>
+        <v>-1.485</v>
       </c>
       <c r="T13" t="n">
-        <v>1.532</v>
+        <v>1.829</v>
       </c>
       <c r="U13" t="n">
-        <v>-3.3141</v>
+        <v>-3.314</v>
       </c>
       <c r="V13" t="n">
         <v>-3.5472</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>5.4255</v>
+        <v>7.1892</v>
       </c>
       <c r="E14" t="n">
-        <v>8.8714</v>
+        <v>10.2018</v>
       </c>
       <c r="F14" t="n">
-        <v>-3.4459</v>
+        <v>-3.0126</v>
       </c>
       <c r="G14" t="n">
         <v>5.4128</v>
@@ -1546,13 +1546,13 @@
         <v>1.5668</v>
       </c>
       <c r="S14" t="n">
-        <v>-1.6492</v>
+        <v>0.1144</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.9328</v>
+        <v>0.3976</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.7165</v>
+        <v>-0.2832</v>
       </c>
       <c r="V14" t="n">
         <v>1.0744</v>
@@ -1567,7 +1567,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A. GAYE</t>
+          <t>R. VARELA BARRAL</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,73 +1579,73 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>1.1418</v>
+        <v>0.7671</v>
       </c>
       <c r="E15" t="n">
-        <v>1.6746</v>
+        <v>1.164</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.5327</v>
+        <v>-0.397</v>
       </c>
       <c r="G15" t="n">
-        <v>1.79</v>
+        <v>0.8337</v>
       </c>
       <c r="H15" t="n">
-        <v>2.1834</v>
+        <v>0.1514</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.3934</v>
+        <v>0.6822</v>
       </c>
       <c r="J15" t="n">
-        <v>2.3702</v>
+        <v>0.89</v>
       </c>
       <c r="K15" t="n">
-        <v>2.249</v>
+        <v>0.08169999999999999</v>
       </c>
       <c r="L15" t="n">
-        <v>0.1212</v>
+        <v>0.8083</v>
       </c>
       <c r="M15" t="n">
-        <v>-0.5803</v>
+        <v>-0.0563</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.06560000000000001</v>
+        <v>0.0698</v>
       </c>
       <c r="O15" t="n">
-        <v>-0.5145999999999999</v>
+        <v>-0.1261</v>
       </c>
       <c r="P15" t="n">
-        <v>-4.1128</v>
+        <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>-4.8962</v>
+        <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>0.7834</v>
+        <v>0</v>
       </c>
       <c r="S15" t="n">
-        <v>2.1905</v>
+        <v>-0.06660000000000001</v>
       </c>
       <c r="T15" t="n">
-        <v>1.7673</v>
+        <v>0.2741</v>
       </c>
       <c r="U15" t="n">
-        <v>0.4232</v>
+        <v>-0.3407</v>
       </c>
       <c r="V15" t="n">
-        <v>1.2742</v>
+        <v>0</v>
       </c>
       <c r="W15" t="n">
-        <v>2.4332</v>
+        <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>-1.159</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>R. VARELA BARRAL</t>
+          <t>A. GAYE</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,67 +1657,67 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>0.2287</v>
+        <v>-0.2142</v>
       </c>
       <c r="E16" t="n">
-        <v>0.6524</v>
+        <v>0.4465</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.4237</v>
+        <v>-0.6608000000000001</v>
       </c>
       <c r="G16" t="n">
-        <v>0.8337</v>
+        <v>1.79</v>
       </c>
       <c r="H16" t="n">
-        <v>0.1514</v>
+        <v>2.1834</v>
       </c>
       <c r="I16" t="n">
-        <v>0.6822</v>
+        <v>-0.3934</v>
       </c>
       <c r="J16" t="n">
-        <v>0.89</v>
+        <v>2.3702</v>
       </c>
       <c r="K16" t="n">
-        <v>0.08169999999999999</v>
+        <v>2.249</v>
       </c>
       <c r="L16" t="n">
-        <v>0.8083</v>
+        <v>0.1212</v>
       </c>
       <c r="M16" t="n">
-        <v>-0.0563</v>
+        <v>-0.5803</v>
       </c>
       <c r="N16" t="n">
-        <v>0.0698</v>
+        <v>-0.06560000000000001</v>
       </c>
       <c r="O16" t="n">
-        <v>-0.1261</v>
+        <v>-0.5145999999999999</v>
       </c>
       <c r="P16" t="n">
-        <v>0</v>
+        <v>-4.1128</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>-4.8962</v>
       </c>
       <c r="R16" t="n">
-        <v>0</v>
+        <v>0.7834</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.605</v>
+        <v>0.8344</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.2376</v>
+        <v>0.5393</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.3674</v>
+        <v>0.2951</v>
       </c>
       <c r="V16" t="n">
-        <v>0</v>
+        <v>1.2742</v>
       </c>
       <c r="W16" t="n">
-        <v>0</v>
+        <v>2.4332</v>
       </c>
       <c r="X16" t="n">
-        <v>0</v>
+        <v>-1.159</v>
       </c>
     </row>
     <row r="17">
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.0519</v>
+        <v>-0.3039</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.2566</v>
+        <v>-0.6659</v>
       </c>
       <c r="F17" t="n">
-        <v>0.3085</v>
+        <v>0.362</v>
       </c>
       <c r="G17" t="n">
         <v>0.3133</v>
@@ -1780,13 +1780,13 @@
         <v>0</v>
       </c>
       <c r="S17" t="n">
-        <v>0.7179</v>
+        <v>0.362</v>
       </c>
       <c r="T17" t="n">
-        <v>0.6822</v>
+        <v>0.2729</v>
       </c>
       <c r="U17" t="n">
-        <v>0.0356</v>
+        <v>0.0891</v>
       </c>
       <c r="V17" t="n">
         <v>0</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.7978</v>
+        <v>-1.1804</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.3156</v>
+        <v>-0.7249</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.4822</v>
+        <v>-0.4555</v>
       </c>
       <c r="G18" t="n">
         <v>-0.2987</v>
@@ -1858,13 +1858,13 @@
         <v>0.5875</v>
       </c>
       <c r="S18" t="n">
-        <v>0.3678</v>
+        <v>-0.0149</v>
       </c>
       <c r="T18" t="n">
-        <v>0.6228</v>
+        <v>0.2135</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.2551</v>
+        <v>-0.2283</v>
       </c>
       <c r="V18" t="n">
         <v>-0.4751</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-2.6242</v>
+        <v>-2.7375</v>
       </c>
       <c r="E19" t="n">
-        <v>0.2577</v>
+        <v>0.4623</v>
       </c>
       <c r="F19" t="n">
-        <v>-2.8819</v>
+        <v>-3.1999</v>
       </c>
       <c r="G19" t="n">
         <v>-2.3334</v>
@@ -1936,13 +1936,13 @@
         <v>1.1751</v>
       </c>
       <c r="S19" t="n">
-        <v>1.0633</v>
+        <v>0.95</v>
       </c>
       <c r="T19" t="n">
-        <v>0.3546</v>
+        <v>0.5593</v>
       </c>
       <c r="U19" t="n">
-        <v>0.7087</v>
+        <v>0.3907</v>
       </c>
       <c r="V19" t="n">
         <v>0.4085</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-3.7591</v>
+        <v>-2.768</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.2919</v>
+        <v>0.3221</v>
       </c>
       <c r="F20" t="n">
-        <v>-3.4671</v>
+        <v>-3.0901</v>
       </c>
       <c r="G20" t="n">
         <v>-2.7289</v>
@@ -2014,13 +2014,13 @@
         <v>1.3709</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.9553</v>
+        <v>0.0357</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.1317</v>
+        <v>0.4823</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.8236</v>
+        <v>-0.4465</v>
       </c>
       <c r="V20" t="n">
         <v>1.492</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-4.0146</v>
+        <v>-3.5694</v>
       </c>
       <c r="E21" t="n">
-        <v>-2.0488</v>
+        <v>-1.8441</v>
       </c>
       <c r="F21" t="n">
-        <v>-1.9658</v>
+        <v>-1.7252</v>
       </c>
       <c r="G21" t="n">
         <v>-3.0921</v>
@@ -2092,13 +2092,13 @@
         <v>0.7834</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.4513</v>
+        <v>-0.006</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.5346</v>
+        <v>-0.3299</v>
       </c>
       <c r="U21" t="n">
-        <v>0.0833</v>
+        <v>0.3239</v>
       </c>
       <c r="V21" t="n">
         <v>-0.2754</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-4.3515</v>
+        <v>-4.4612</v>
       </c>
       <c r="E22" t="n">
-        <v>-2.4083</v>
+        <v>-2.8176</v>
       </c>
       <c r="F22" t="n">
-        <v>-1.9432</v>
+        <v>-1.6436</v>
       </c>
       <c r="G22" t="n">
         <v>-5.517</v>
@@ -2170,13 +2170,13 @@
         <v>1.5668</v>
       </c>
       <c r="S22" t="n">
-        <v>0.4448</v>
+        <v>0.3351</v>
       </c>
       <c r="T22" t="n">
-        <v>0.7287</v>
+        <v>0.3194</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.2839</v>
+        <v>0.0157</v>
       </c>
       <c r="V22" t="n">
         <v>0.1332</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-5.5241</v>
+        <v>-5.5803</v>
       </c>
       <c r="E23" t="n">
-        <v>-1.3596</v>
+        <v>-1.7689</v>
       </c>
       <c r="F23" t="n">
-        <v>-4.1645</v>
+        <v>-3.8114</v>
       </c>
       <c r="G23" t="n">
         <v>-5.1189</v>
@@ -2248,13 +2248,13 @@
         <v>1.9585</v>
       </c>
       <c r="S23" t="n">
-        <v>0.6587</v>
+        <v>0.6024</v>
       </c>
       <c r="T23" t="n">
-        <v>0.9951</v>
+        <v>0.5858</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.3365</v>
+        <v>0.0166</v>
       </c>
       <c r="V23" t="n">
         <v>-0.08459999999999999</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-14.2234</v>
+        <v>-12.8586</v>
       </c>
       <c r="E24" t="n">
-        <v>4.775299999999998</v>
+        <v>4.7753</v>
       </c>
       <c r="F24" t="n">
-        <v>-18.9985</v>
+        <v>-17.6341</v>
       </c>
       <c r="G24" t="n">
         <v>-10.7392</v>
@@ -2317,7 +2317,7 @@
         <v>-13.9116</v>
       </c>
       <c r="P24" t="n">
-        <v>-8.8131</v>
+        <v>-8.813099999999999</v>
       </c>
       <c r="Q24" t="n">
         <v>-18.6053</v>
@@ -2326,13 +2326,13 @@
         <v>9.792400000000001</v>
       </c>
       <c r="S24" t="n">
-        <v>1.7822</v>
+        <v>3.146500000000001</v>
       </c>
       <c r="T24" t="n">
-        <v>3.314</v>
+        <v>3.3143</v>
       </c>
       <c r="U24" t="n">
-        <v>-1.5322</v>
+        <v>-0.1676</v>
       </c>
       <c r="V24" t="n">
         <v>3.547200000000001</v>
